--- a/artfynd/A 31198-2023 artfynd.xlsx
+++ b/artfynd/A 31198-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>133850733</v>
       </c>
       <c r="B4" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>133851071</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>133850986</v>
       </c>
       <c r="B11" t="n">
-        <v>79438</v>
+        <v>79445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>133850732</v>
       </c>
       <c r="B13" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31198-2023 artfynd.xlsx
+++ b/artfynd/A 31198-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115413246</v>
+        <v>133850986</v>
       </c>
       <c r="B2" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hidberget, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574662</v>
+        <v>574660</v>
       </c>
       <c r="R2" t="n">
-        <v>7205645</v>
+        <v>7205646</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-83</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +765,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115417721</v>
+        <v>133851071</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -823,17 +808,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hidberget, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574702</v>
+        <v>574570</v>
       </c>
       <c r="R3" t="n">
-        <v>7205651</v>
+        <v>7205645</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:17</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:17</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-74</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,60 +867,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133850733</v>
+        <v>115417719</v>
       </c>
       <c r="B4" t="n">
-        <v>83351</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574694</v>
+        <v>574625</v>
       </c>
       <c r="R4" t="n">
-        <v>7205649</v>
+        <v>7205655</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,17 +944,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-90</t>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,26 +974,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133851071</v>
+        <v>115417720</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1032,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574570</v>
+        <v>574656</v>
       </c>
       <c r="R5" t="n">
-        <v>7205645</v>
+        <v>7205640</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,17 +1051,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-74</t>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,31 +1081,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115417719</v>
+        <v>115417721</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1143,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574625</v>
+        <v>574702</v>
       </c>
       <c r="R6" t="n">
-        <v>7205655</v>
+        <v>7205651</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1178,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,45 +1200,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115413261</v>
+        <v>115417722</v>
       </c>
       <c r="B7" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hidberget, Ås lm</t>
@@ -1263,7 +1238,7 @@
         <v>574790</v>
       </c>
       <c r="R7" t="n">
-        <v>7205661</v>
+        <v>7205665</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1332,15 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115413260</v>
+        <v>115413246</v>
       </c>
       <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,39 +1318,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574621</v>
+        <v>574662</v>
       </c>
       <c r="R8" t="n">
-        <v>7205656</v>
+        <v>7205645</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1412,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,15 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115417720</v>
+        <v>133850733</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,37 +1425,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hidberget, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574656</v>
+        <v>574694</v>
       </c>
       <c r="R9" t="n">
-        <v>7205640</v>
+        <v>7205649</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,22 +1479,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-90</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,27 +1504,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115417722</v>
+        <v>133850732</v>
       </c>
       <c r="B10" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,37 +1527,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hidberget, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574790</v>
+        <v>574662</v>
       </c>
       <c r="R10" t="n">
-        <v>7205665</v>
+        <v>7205646</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,22 +1581,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-91</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,22 +1606,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133850986</v>
+        <v>115413259</v>
       </c>
       <c r="B11" t="n">
-        <v>79445</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,37 +1629,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574660</v>
+        <v>574570</v>
       </c>
       <c r="R11" t="n">
-        <v>7205646</v>
+        <v>7205645</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,17 +1688,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-83</t>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,27 +1718,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115413259</v>
+        <v>115413260</v>
       </c>
       <c r="B12" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574570</v>
+        <v>574621</v>
       </c>
       <c r="R12" t="n">
-        <v>7205645</v>
+        <v>7205656</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1855,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133850732</v>
+        <v>115413261</v>
       </c>
       <c r="B13" t="n">
-        <v>83351</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,37 +1853,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574662</v>
+        <v>574790</v>
       </c>
       <c r="R13" t="n">
-        <v>7205646</v>
+        <v>7205661</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1957,17 +1912,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-91</t>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,12 +1942,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
